--- a/resources/templates/standard/F2100-13.xlsx
+++ b/resources/templates/standard/F2100-13.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>사내 자격인증 평가서</t>
   </si>
@@ -638,11 +641,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -675,20 +680,20 @@
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ1" s="4"/>
       <c r="AR1" s="4"/>
@@ -787,25 +792,25 @@
     </row>
     <row r="4" ht="19.9" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -832,13 +837,13 @@
       <c r="AJ4" s="7"/>
       <c r="AK4" s="7"/>
       <c r="AL4" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM4" s="7"/>
       <c r="AN4" s="7"/>
       <c r="AO4" s="7"/>
       <c r="AP4" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4" s="7"/>
       <c r="AR4" s="7"/>
@@ -857,37 +862,37 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V5" s="8"/>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
       <c r="Y5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
       <c r="AC5" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
       <c r="AF5" s="8"/>
       <c r="AG5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH5" s="8"/>
       <c r="AI5" s="8"/>
@@ -1353,7 +1358,7 @@
     </row>
     <row r="15" ht="34.9" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -1401,7 +1406,7 @@
     </row>
     <row r="16" ht="34.9" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -1449,7 +1454,7 @@
     </row>
     <row r="17" ht="34.9" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
